--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -62868,21 +62868,44 @@
         <v>46276.2916666667</v>
       </c>
       <c r="B2718" t="n">
+        <v>200886800</v>
+      </c>
+      <c r="C2718" t="n">
+        <v>52530</v>
+      </c>
+      <c r="D2718" t="n">
+        <v>51995</v>
+      </c>
+      <c r="E2718" t="n">
+        <v>52096</v>
+      </c>
+      <c r="F2718" t="n">
+        <v>52512</v>
+      </c>
+      <c r="G2718" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
         <v>0</v>
       </c>
-      <c r="C2718" t="n">
-        <v>52529.921875</v>
-      </c>
-      <c r="D2718" t="n">
-        <v>51994.7890625</v>
-      </c>
-      <c r="E2718" t="n">
-        <v>52095.8984375</v>
-      </c>
-      <c r="F2718" t="n">
-        <v>52512.03125</v>
-      </c>
-      <c r="G2718" t="s">
+      <c r="C2719" t="n">
+        <v>52378.2890625</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>51465.078125</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>52262.55859375</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>51628.76953125</v>
+      </c>
+      <c r="G2719" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -62891,21 +62891,44 @@
         <v>46279.2916666667</v>
       </c>
       <c r="B2719" t="n">
+        <v>232299500</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>52378</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>51465</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>52263</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>51629</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
         <v>0</v>
       </c>
-      <c r="C2719" t="n">
-        <v>52378.2890625</v>
-      </c>
-      <c r="D2719" t="n">
-        <v>51465.078125</v>
-      </c>
-      <c r="E2719" t="n">
-        <v>52262.55859375</v>
-      </c>
-      <c r="F2719" t="n">
-        <v>51628.76953125</v>
-      </c>
-      <c r="G2719" t="s">
+      <c r="C2720" t="n">
+        <v>51789.828125</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>50819.2890625</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>51321.51953125</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>51555.19140625</v>
+      </c>
+      <c r="G2720" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -62914,21 +62914,44 @@
         <v>46280.2916666667</v>
       </c>
       <c r="B2720" t="n">
+        <v>202624900</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>51790</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>50819</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>51322</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>51555</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
         <v>0</v>
       </c>
-      <c r="C2720" t="n">
-        <v>51789.828125</v>
-      </c>
-      <c r="D2720" t="n">
-        <v>50819.2890625</v>
-      </c>
-      <c r="E2720" t="n">
-        <v>51321.51953125</v>
-      </c>
-      <c r="F2720" t="n">
-        <v>51555.19140625</v>
-      </c>
-      <c r="G2720" t="s">
+      <c r="C2721" t="n">
+        <v>52091.8984375</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>51685.01171875</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>51787.921875</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>51969.12109375</v>
+      </c>
+      <c r="G2721" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -62937,21 +62937,44 @@
         <v>46281.2916666667</v>
       </c>
       <c r="B2721" t="n">
+        <v>219762800</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>52092</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>51685</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>51788</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>51969</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
         <v>0</v>
       </c>
-      <c r="C2721" t="n">
-        <v>52091.8984375</v>
-      </c>
-      <c r="D2721" t="n">
-        <v>51685.01171875</v>
-      </c>
-      <c r="E2721" t="n">
-        <v>51787.921875</v>
-      </c>
-      <c r="F2721" t="n">
-        <v>51969.12109375</v>
-      </c>
-      <c r="G2721" t="s">
+      <c r="C2722" t="n">
+        <v>52483.37109375</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>52046.3515625</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>52193.2890625</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>52385.5</v>
+      </c>
+      <c r="G2722" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -62960,21 +62960,44 @@
         <v>46282.2916666667</v>
       </c>
       <c r="B2722" t="n">
+        <v>222489600</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>52483</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>52046</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>52193</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>52386</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
         <v>0</v>
       </c>
-      <c r="C2722" t="n">
-        <v>52483.37109375</v>
-      </c>
-      <c r="D2722" t="n">
-        <v>52046.3515625</v>
-      </c>
-      <c r="E2722" t="n">
-        <v>52193.2890625</v>
-      </c>
-      <c r="F2722" t="n">
-        <v>52385.5</v>
-      </c>
-      <c r="G2722" t="s">
+      <c r="C2723" t="n">
+        <v>52341.69140625</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>51446.5</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>52341.69140625</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>51545.25</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -62983,21 +62983,44 @@
         <v>46283.2916666667</v>
       </c>
       <c r="B2723" t="n">
+        <v>615043100</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>52342</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>51447</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>52342</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>51545</v>
+      </c>
+      <c r="G2723" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2724">
+      <c r="A2724" s="1" t="n">
+        <v>46286.2916666667</v>
+      </c>
+      <c r="B2724" t="n">
         <v>0</v>
       </c>
-      <c r="C2723" t="n">
-        <v>52341.69140625</v>
-      </c>
-      <c r="D2723" t="n">
-        <v>51446.5</v>
-      </c>
-      <c r="E2723" t="n">
-        <v>52341.69140625</v>
-      </c>
-      <c r="F2723" t="n">
-        <v>51545.25</v>
-      </c>
-      <c r="G2723" t="s">
+      <c r="C2724" t="n">
+        <v>52407.4609375</v>
+      </c>
+      <c r="D2724" t="n">
+        <v>51787.91015625</v>
+      </c>
+      <c r="E2724" t="n">
+        <v>51814.921875</v>
+      </c>
+      <c r="F2724" t="n">
+        <v>52371.5390625</v>
+      </c>
+      <c r="G2724" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -63006,21 +63006,44 @@
         <v>46286.2916666667</v>
       </c>
       <c r="B2724" t="n">
+        <v>178799300</v>
+      </c>
+      <c r="C2724" t="n">
+        <v>52407</v>
+      </c>
+      <c r="D2724" t="n">
+        <v>51788</v>
+      </c>
+      <c r="E2724" t="n">
+        <v>51815</v>
+      </c>
+      <c r="F2724" t="n">
+        <v>52372</v>
+      </c>
+      <c r="G2724" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2725">
+      <c r="A2725" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2725" t="n">
         <v>0</v>
       </c>
-      <c r="C2724" t="n">
-        <v>52407.4609375</v>
-      </c>
-      <c r="D2724" t="n">
-        <v>51787.91015625</v>
-      </c>
-      <c r="E2724" t="n">
-        <v>51814.921875</v>
-      </c>
-      <c r="F2724" t="n">
-        <v>52371.5390625</v>
-      </c>
-      <c r="G2724" t="s">
+      <c r="C2725" t="n">
+        <v>52445.6796875</v>
+      </c>
+      <c r="D2725" t="n">
+        <v>51931.30859375</v>
+      </c>
+      <c r="E2725" t="n">
+        <v>52421.6796875</v>
+      </c>
+      <c r="F2725" t="n">
+        <v>52095.828125</v>
+      </c>
+      <c r="G2725" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -63026,22 +63026,22 @@
     </row>
     <row r="2725">
       <c r="A2725" s="1" t="n">
-        <v>46287.2916666667</v>
+        <v>46288.2916666667</v>
       </c>
       <c r="B2725" t="n">
         <v>0</v>
       </c>
       <c r="C2725" t="n">
-        <v>52445.6796875</v>
+        <v>52525.109375</v>
       </c>
       <c r="D2725" t="n">
-        <v>51931.30859375</v>
+        <v>51775.48828125</v>
       </c>
       <c r="E2725" t="n">
-        <v>52421.6796875</v>
+        <v>52349.578125</v>
       </c>
       <c r="F2725" t="n">
-        <v>52095.828125</v>
+        <v>51987.48828125</v>
       </c>
       <c r="G2725" t="s">
         <v>7</v>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -63029,21 +63029,44 @@
         <v>46288.2916666667</v>
       </c>
       <c r="B2725" t="n">
+        <v>191784200</v>
+      </c>
+      <c r="C2725" t="n">
+        <v>52525</v>
+      </c>
+      <c r="D2725" t="n">
+        <v>51775</v>
+      </c>
+      <c r="E2725" t="n">
+        <v>52350</v>
+      </c>
+      <c r="F2725" t="n">
+        <v>51987</v>
+      </c>
+      <c r="G2725" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
         <v>0</v>
       </c>
-      <c r="C2725" t="n">
-        <v>52525.109375</v>
-      </c>
-      <c r="D2725" t="n">
-        <v>51775.48828125</v>
-      </c>
-      <c r="E2725" t="n">
-        <v>52349.578125</v>
-      </c>
-      <c r="F2725" t="n">
-        <v>51987.48828125</v>
-      </c>
-      <c r="G2725" t="s">
+      <c r="C2726" t="n">
+        <v>51994.98046875</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>51539.5</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>51687.33984375</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>51543.44921875</v>
+      </c>
+      <c r="G2726" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -63026,22 +63026,22 @@
     </row>
     <row r="2725">
       <c r="A2725" s="1" t="n">
-        <v>46288.2916666667</v>
+        <v>46287.2916666667</v>
       </c>
       <c r="B2725" t="n">
-        <v>191784200</v>
+        <v>229482600</v>
       </c>
       <c r="C2725" t="n">
-        <v>52525</v>
+        <v>52446</v>
       </c>
       <c r="D2725" t="n">
-        <v>51775</v>
+        <v>51931</v>
       </c>
       <c r="E2725" t="n">
-        <v>52350</v>
+        <v>52422</v>
       </c>
       <c r="F2725" t="n">
-        <v>51987</v>
+        <v>52096</v>
       </c>
       <c r="G2725" t="s">
         <v>7</v>
@@ -63049,24 +63049,70 @@
     </row>
     <row r="2726">
       <c r="A2726" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>191784200</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>52525</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>51775</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>52350</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>51987</v>
+      </c>
+      <c r="G2726" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
         <v>46289.2916666667</v>
       </c>
-      <c r="B2726" t="n">
+      <c r="B2727" t="n">
+        <v>199398800</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>51995</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>51540</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>51687</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>51543</v>
+      </c>
+      <c r="G2727" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
         <v>0</v>
       </c>
-      <c r="C2726" t="n">
-        <v>51994.98046875</v>
-      </c>
-      <c r="D2726" t="n">
-        <v>51539.5</v>
-      </c>
-      <c r="E2726" t="n">
-        <v>51687.33984375</v>
-      </c>
-      <c r="F2726" t="n">
-        <v>51543.44921875</v>
-      </c>
-      <c r="G2726" t="s">
+      <c r="C2728" t="n">
+        <v>52209.87890625</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>51657.96875</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>52044.25</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>51866.9296875</v>
+      </c>
+      <c r="G2728" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -63098,21 +63098,42 @@
         <v>46290.2916666667</v>
       </c>
       <c r="B2728" t="n">
+        <v>186973800</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>52210</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>51658</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>52044</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>51867</v>
+      </c>
+      <c r="G2728" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
         <v>0</v>
       </c>
-      <c r="C2728" t="n">
-        <v>52209.87890625</v>
-      </c>
-      <c r="D2728" t="n">
-        <v>51657.96875</v>
-      </c>
-      <c r="E2728" t="n">
-        <v>52044.25</v>
-      </c>
-      <c r="F2728" t="n">
-        <v>51866.9296875</v>
-      </c>
-      <c r="G2728" t="s">
+      <c r="C2729" t="n">
+        <v>52210.26953125</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>51749.80859375</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>51913.73828125</v>
+      </c>
+      <c r="F2729"/>
+      <c r="G2729" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -63121,19 +63121,44 @@
         <v>46293.2916666667</v>
       </c>
       <c r="B2729" t="n">
+        <v>193999600</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>52210</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>51750</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>51914</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>51760</v>
+      </c>
+      <c r="G2729" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2730">
+      <c r="A2730" s="1" t="n">
+        <v>46294.2916666667</v>
+      </c>
+      <c r="B2730" t="n">
         <v>0</v>
       </c>
-      <c r="C2729" t="n">
-        <v>52210.26953125</v>
-      </c>
-      <c r="D2729" t="n">
-        <v>51749.80859375</v>
-      </c>
-      <c r="E2729" t="n">
-        <v>51913.73828125</v>
-      </c>
-      <c r="F2729"/>
-      <c r="G2729" t="s">
+      <c r="C2730" t="n">
+        <v>52289.66015625</v>
+      </c>
+      <c r="D2730" t="n">
+        <v>51700.83984375</v>
+      </c>
+      <c r="E2730" t="n">
+        <v>51915.9296875</v>
+      </c>
+      <c r="F2730" t="n">
+        <v>51804.94140625</v>
+      </c>
+      <c r="G2730" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -63144,21 +63144,42 @@
         <v>46294.2916666667</v>
       </c>
       <c r="B2730" t="n">
+        <v>210118900</v>
+      </c>
+      <c r="C2730" t="n">
+        <v>52290</v>
+      </c>
+      <c r="D2730" t="n">
+        <v>51701</v>
+      </c>
+      <c r="E2730" t="n">
+        <v>51916</v>
+      </c>
+      <c r="F2730" t="n">
+        <v>51805</v>
+      </c>
+      <c r="G2730" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2731">
+      <c r="A2731" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2731" t="n">
         <v>0</v>
       </c>
-      <c r="C2730" t="n">
-        <v>52289.66015625</v>
-      </c>
-      <c r="D2730" t="n">
-        <v>51700.83984375</v>
-      </c>
-      <c r="E2730" t="n">
-        <v>51915.9296875</v>
-      </c>
-      <c r="F2730" t="n">
-        <v>51804.94140625</v>
-      </c>
-      <c r="G2730" t="s">
+      <c r="C2731" t="n">
+        <v>52212.94921875</v>
+      </c>
+      <c r="D2731" t="n">
+        <v>51288.98046875</v>
+      </c>
+      <c r="E2731" t="n">
+        <v>51861.3203125</v>
+      </c>
+      <c r="F2731"/>
+      <c r="G2731" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -63167,19 +63167,42 @@
         <v>46295.2916666667</v>
       </c>
       <c r="B2731" t="n">
+        <v>382302300</v>
+      </c>
+      <c r="C2731" t="n">
+        <v>52213</v>
+      </c>
+      <c r="D2731" t="n">
+        <v>51289</v>
+      </c>
+      <c r="E2731" t="n">
+        <v>51861</v>
+      </c>
+      <c r="F2731" t="n">
+        <v>51372</v>
+      </c>
+      <c r="G2731" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
         <v>0</v>
       </c>
-      <c r="C2731" t="n">
-        <v>52212.94921875</v>
-      </c>
-      <c r="D2731" t="n">
-        <v>51288.98046875</v>
-      </c>
-      <c r="E2731" t="n">
-        <v>51861.3203125</v>
-      </c>
-      <c r="F2731"/>
-      <c r="G2731" t="s">
+      <c r="C2732" t="n">
+        <v>51209.30078125</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>50237.859375</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>50971.48828125</v>
+      </c>
+      <c r="F2732"/>
+      <c r="G2732" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -63190,19 +63190,44 @@
         <v>46296.2916666667</v>
       </c>
       <c r="B2732" t="n">
+        <v>305633900</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>51209</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>50238</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>50971</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>50238</v>
+      </c>
+      <c r="G2732" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2733">
+      <c r="A2733" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B2733" t="n">
         <v>0</v>
       </c>
-      <c r="C2732" t="n">
-        <v>51209.30078125</v>
-      </c>
-      <c r="D2732" t="n">
-        <v>50237.859375</v>
-      </c>
-      <c r="E2732" t="n">
-        <v>50971.48828125</v>
-      </c>
-      <c r="F2732"/>
-      <c r="G2732" t="s">
+      <c r="C2733" t="n">
+        <v>50694.66015625</v>
+      </c>
+      <c r="D2733" t="n">
+        <v>49972.2890625</v>
+      </c>
+      <c r="E2733" t="n">
+        <v>50364.08984375</v>
+      </c>
+      <c r="F2733" t="n">
+        <v>50483.2109375</v>
+      </c>
+      <c r="G2733" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -63213,21 +63213,42 @@
         <v>46297.2916666667</v>
       </c>
       <c r="B2733" t="n">
+        <v>338834800</v>
+      </c>
+      <c r="C2733" t="n">
+        <v>50695</v>
+      </c>
+      <c r="D2733" t="n">
+        <v>49972</v>
+      </c>
+      <c r="E2733" t="n">
+        <v>50364</v>
+      </c>
+      <c r="F2733" t="n">
+        <v>50483</v>
+      </c>
+      <c r="G2733" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2734">
+      <c r="A2734" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B2734" t="n">
         <v>0</v>
       </c>
-      <c r="C2733" t="n">
-        <v>50694.66015625</v>
-      </c>
-      <c r="D2733" t="n">
-        <v>49972.2890625</v>
-      </c>
-      <c r="E2733" t="n">
-        <v>50364.08984375</v>
-      </c>
-      <c r="F2733" t="n">
-        <v>50483.2109375</v>
-      </c>
-      <c r="G2733" t="s">
+      <c r="C2734" t="n">
+        <v>50842.69140625</v>
+      </c>
+      <c r="D2734" t="n">
+        <v>50303.23828125</v>
+      </c>
+      <c r="E2734" t="n">
+        <v>50506.73828125</v>
+      </c>
+      <c r="F2734"/>
+      <c r="G2734" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -63236,19 +63236,42 @@
         <v>46300.2916666667</v>
       </c>
       <c r="B2734" t="n">
+        <v>251347700</v>
+      </c>
+      <c r="C2734" t="n">
+        <v>50843</v>
+      </c>
+      <c r="D2734" t="n">
+        <v>50303</v>
+      </c>
+      <c r="E2734" t="n">
+        <v>50507</v>
+      </c>
+      <c r="F2734" t="n">
+        <v>50818</v>
+      </c>
+      <c r="G2734" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2735">
+      <c r="A2735" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2735" t="n">
         <v>0</v>
       </c>
-      <c r="C2734" t="n">
-        <v>50842.69140625</v>
-      </c>
-      <c r="D2734" t="n">
-        <v>50303.23828125</v>
-      </c>
-      <c r="E2734" t="n">
-        <v>50506.73828125</v>
-      </c>
-      <c r="F2734"/>
-      <c r="G2734" t="s">
+      <c r="C2735" t="n">
+        <v>51565.6484375</v>
+      </c>
+      <c r="D2735" t="n">
+        <v>51044.5</v>
+      </c>
+      <c r="E2735" t="n">
+        <v>51098.3984375</v>
+      </c>
+      <c r="F2735"/>
+      <c r="G2735" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -63259,19 +63259,42 @@
         <v>46301.2916666667</v>
       </c>
       <c r="B2735" t="n">
+        <v>256779000</v>
+      </c>
+      <c r="C2735" t="n">
+        <v>51566</v>
+      </c>
+      <c r="D2735" t="n">
+        <v>51045</v>
+      </c>
+      <c r="E2735" t="n">
+        <v>51098</v>
+      </c>
+      <c r="F2735" t="n">
+        <v>51261</v>
+      </c>
+      <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
         <v>0</v>
       </c>
-      <c r="C2735" t="n">
-        <v>51565.6484375</v>
-      </c>
-      <c r="D2735" t="n">
-        <v>51044.5</v>
-      </c>
-      <c r="E2735" t="n">
-        <v>51098.3984375</v>
-      </c>
-      <c r="F2735"/>
-      <c r="G2735" t="s">
+      <c r="C2736" t="n">
+        <v>51043.41015625</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>49820.6484375</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>50918.140625</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -63282,19 +63282,42 @@
         <v>46302.2916666667</v>
       </c>
       <c r="B2736" t="n">
+        <v>279244000</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>51043</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>49821</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>50918</v>
+      </c>
+      <c r="F2736" t="n">
+        <v>49972</v>
+      </c>
+      <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
         <v>0</v>
       </c>
-      <c r="C2736" t="n">
-        <v>51043.41015625</v>
-      </c>
-      <c r="D2736" t="n">
-        <v>49820.6484375</v>
-      </c>
-      <c r="E2736" t="n">
-        <v>50918.140625</v>
-      </c>
-      <c r="F2736"/>
-      <c r="G2736" t="s">
+      <c r="C2737" t="n">
+        <v>49729.94921875</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>49105.890625</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>49269.16015625</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -63305,19 +63305,42 @@
         <v>46303.2916666667</v>
       </c>
       <c r="B2737" t="n">
+        <v>279405500</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>49730</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>49106</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>49269</v>
+      </c>
+      <c r="F2737" t="n">
+        <v>49298</v>
+      </c>
+      <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
         <v>0</v>
       </c>
-      <c r="C2737" t="n">
-        <v>49729.94921875</v>
-      </c>
-      <c r="D2737" t="n">
-        <v>49105.890625</v>
-      </c>
-      <c r="E2737" t="n">
-        <v>49269.16015625</v>
-      </c>
-      <c r="F2737"/>
-      <c r="G2737" t="s">
+      <c r="C2738" t="n">
+        <v>49916.62890625</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>49572.96875</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>49704.37109375</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -63328,18 +63328,20 @@
         <v>46304.2916666667</v>
       </c>
       <c r="B2738" t="n">
-        <v>0</v>
+        <v>219575600</v>
       </c>
       <c r="C2738" t="n">
-        <v>49916.62890625</v>
+        <v>49917</v>
       </c>
       <c r="D2738" t="n">
-        <v>49572.96875</v>
+        <v>49573</v>
       </c>
       <c r="E2738" t="n">
-        <v>49704.37109375</v>
-      </c>
-      <c r="F2738"/>
+        <v>49704</v>
+      </c>
+      <c r="F2738" t="n">
+        <v>49746</v>
+      </c>
       <c r="G2738" t="s">
         <v>7</v>
       </c>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -63346,6 +63346,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>193534700</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>50280</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>49908</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>50064</v>
+      </c>
+      <c r="F2739" t="n">
+        <v>50035</v>
+      </c>
+      <c r="G2739" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -63369,6 +63369,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>179982500</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>50381</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>49973</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>50102</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>50057</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2741">
+      <c r="A2741" s="1" t="n">
+        <v>46309.2916666667</v>
+      </c>
+      <c r="B2741" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2741" t="n">
+        <v>50244.3203125</v>
+      </c>
+      <c r="D2741" t="n">
+        <v>49677.9609375</v>
+      </c>
+      <c r="E2741" t="n">
+        <v>50202.7109375</v>
+      </c>
+      <c r="F2741" t="n">
+        <v>49753.83984375</v>
+      </c>
+      <c r="G2741" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -63397,21 +63397,44 @@
         <v>46309.2916666667</v>
       </c>
       <c r="B2741" t="n">
+        <v>217570200</v>
+      </c>
+      <c r="C2741" t="n">
+        <v>50244</v>
+      </c>
+      <c r="D2741" t="n">
+        <v>49678</v>
+      </c>
+      <c r="E2741" t="n">
+        <v>50203</v>
+      </c>
+      <c r="F2741" t="n">
+        <v>49754</v>
+      </c>
+      <c r="G2741" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2742">
+      <c r="A2742" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2742" t="n">
         <v>0</v>
       </c>
-      <c r="C2741" t="n">
-        <v>50244.3203125</v>
-      </c>
-      <c r="D2741" t="n">
-        <v>49677.9609375</v>
-      </c>
-      <c r="E2741" t="n">
-        <v>50202.7109375</v>
-      </c>
-      <c r="F2741" t="n">
-        <v>49753.83984375</v>
-      </c>
-      <c r="G2741" t="s">
+      <c r="C2742" t="n">
+        <v>49742.578125</v>
+      </c>
+      <c r="D2742" t="n">
+        <v>49061.62890625</v>
+      </c>
+      <c r="E2742" t="n">
+        <v>49602.01953125</v>
+      </c>
+      <c r="F2742" t="n">
+        <v>49397.55078125</v>
+      </c>
+      <c r="G2742" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -63420,21 +63420,44 @@
         <v>46310.2916666667</v>
       </c>
       <c r="B2742" t="n">
+        <v>255071700</v>
+      </c>
+      <c r="C2742" t="n">
+        <v>49743</v>
+      </c>
+      <c r="D2742" t="n">
+        <v>49062</v>
+      </c>
+      <c r="E2742" t="n">
+        <v>49602</v>
+      </c>
+      <c r="F2742" t="n">
+        <v>49398</v>
+      </c>
+      <c r="G2742" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
         <v>0</v>
       </c>
-      <c r="C2742" t="n">
-        <v>49742.578125</v>
-      </c>
-      <c r="D2742" t="n">
-        <v>49061.62890625</v>
-      </c>
-      <c r="E2742" t="n">
-        <v>49602.01953125</v>
-      </c>
-      <c r="F2742" t="n">
-        <v>49397.55078125</v>
-      </c>
-      <c r="G2742" t="s">
+      <c r="C2743" t="n">
+        <v>49926.73046875</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>49581.51171875</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>49638.3984375</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>49857.1796875</v>
+      </c>
+      <c r="G2743" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -79925,6 +79925,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2744">
+      <c r="A2744" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2744" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>49515</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>49592</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>48836</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>49086</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>49086</v>
+      </c>
+      <c r="H2744" t="n">
+        <v>216849900</v>
+      </c>
+      <c r="I2744" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="A2745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2745" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2745" t="n">
+        <v>48903.87890625</v>
+      </c>
+      <c r="D2745" t="n">
+        <v>49333.53125</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>48474.19921875</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>49071.37109375</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>49071.37109375</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -79962,24 +79962,53 @@
         <v>46315.2916666667</v>
       </c>
       <c r="C2745" t="n">
-        <v>48903.87890625</v>
+        <v>48904</v>
       </c>
       <c r="D2745" t="n">
-        <v>49333.53125</v>
+        <v>49334</v>
       </c>
       <c r="E2745" t="n">
-        <v>48474.19921875</v>
+        <v>48474</v>
       </c>
       <c r="F2745" t="n">
-        <v>49071.37109375</v>
+        <v>49071</v>
       </c>
       <c r="G2745" t="n">
-        <v>49071.37109375</v>
+        <v>49071</v>
       </c>
       <c r="H2745" t="n">
+        <v>228820700</v>
+      </c>
+      <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>49224.19921875</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>49728.4296875</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>48982.12890625</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>49643.69140625</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>49643.69140625</v>
+      </c>
+      <c r="H2746" t="n">
         <v>0</v>
       </c>
-      <c r="I2745" t="s">
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -79991,24 +79991,53 @@
         <v>46316.2916666667</v>
       </c>
       <c r="C2746" t="n">
-        <v>49224.19921875</v>
+        <v>49224</v>
       </c>
       <c r="D2746" t="n">
-        <v>49728.4296875</v>
+        <v>49728</v>
       </c>
       <c r="E2746" t="n">
-        <v>48982.12890625</v>
+        <v>48982</v>
       </c>
       <c r="F2746" t="n">
-        <v>49643.69140625</v>
+        <v>49644</v>
       </c>
       <c r="G2746" t="n">
-        <v>49643.69140625</v>
+        <v>49644</v>
       </c>
       <c r="H2746" t="n">
+        <v>169897800</v>
+      </c>
+      <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>49191.12109375</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>49235.83984375</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>48363.3515625</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>48383.66015625</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>48383.66015625</v>
+      </c>
+      <c r="H2747" t="n">
         <v>0</v>
       </c>
-      <c r="I2746" t="s">
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -80020,24 +80020,53 @@
         <v>46317.2916666667</v>
       </c>
       <c r="C2747" t="n">
-        <v>49191.12109375</v>
+        <v>49191</v>
       </c>
       <c r="D2747" t="n">
-        <v>49235.83984375</v>
+        <v>49236</v>
       </c>
       <c r="E2747" t="n">
-        <v>48363.3515625</v>
+        <v>48363</v>
       </c>
       <c r="F2747" t="n">
-        <v>48383.66015625</v>
+        <v>48384</v>
       </c>
       <c r="G2747" t="n">
-        <v>48383.66015625</v>
+        <v>48384</v>
       </c>
       <c r="H2747" t="n">
+        <v>241556800</v>
+      </c>
+      <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>48577.83984375</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>48638.19140625</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>48024.26953125</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>48558.859375</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>48558.859375</v>
+      </c>
+      <c r="H2748" t="n">
         <v>0</v>
       </c>
-      <c r="I2747" t="s">
+      <c r="I2748" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -80049,24 +80049,53 @@
         <v>46318.2916666667</v>
       </c>
       <c r="C2748" t="n">
-        <v>48577.83984375</v>
+        <v>48578</v>
       </c>
       <c r="D2748" t="n">
-        <v>48638.19140625</v>
+        <v>48638</v>
       </c>
       <c r="E2748" t="n">
-        <v>48024.26953125</v>
+        <v>48024</v>
       </c>
       <c r="F2748" t="n">
-        <v>48558.859375</v>
+        <v>48559</v>
       </c>
       <c r="G2748" t="n">
-        <v>48558.859375</v>
+        <v>48559</v>
       </c>
       <c r="H2748" t="n">
+        <v>252902600</v>
+      </c>
+      <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>48714.37109375</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>49243.33984375</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>48674.46875</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>49186.80859375</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>49186.80859375</v>
+      </c>
+      <c r="H2749" t="n">
         <v>0</v>
       </c>
-      <c r="I2748" t="s">
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -80078,24 +80078,53 @@
         <v>46321.3333333333</v>
       </c>
       <c r="C2749" t="n">
-        <v>48714.37109375</v>
+        <v>48714</v>
       </c>
       <c r="D2749" t="n">
-        <v>49243.33984375</v>
+        <v>49243</v>
       </c>
       <c r="E2749" t="n">
-        <v>48674.46875</v>
+        <v>48674</v>
       </c>
       <c r="F2749" t="n">
-        <v>49186.80859375</v>
+        <v>49187</v>
       </c>
       <c r="G2749" t="n">
-        <v>49186.80859375</v>
+        <v>49187</v>
       </c>
       <c r="H2749" t="n">
+        <v>210615200</v>
+      </c>
+      <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>48963.890625</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>49658.01953125</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>48927.98828125</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>49627.94921875</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>49627.94921875</v>
+      </c>
+      <c r="H2750" t="n">
         <v>0</v>
       </c>
-      <c r="I2749" t="s">
+      <c r="I2750" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -80107,24 +80107,53 @@
         <v>46322.3333333333</v>
       </c>
       <c r="C2750" t="n">
-        <v>48963.890625</v>
+        <v>48964</v>
       </c>
       <c r="D2750" t="n">
-        <v>49658.01953125</v>
+        <v>49658</v>
       </c>
       <c r="E2750" t="n">
-        <v>48927.98828125</v>
+        <v>48928</v>
       </c>
       <c r="F2750" t="n">
-        <v>49627.94921875</v>
+        <v>49628</v>
       </c>
       <c r="G2750" t="n">
-        <v>49627.94921875</v>
+        <v>49628</v>
       </c>
       <c r="H2750" t="n">
+        <v>210248000</v>
+      </c>
+      <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>49778.3515625</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>49857.5703125</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>49417.75</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>49824.30078125</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>49824.30078125</v>
+      </c>
+      <c r="H2751" t="n">
         <v>0</v>
       </c>
-      <c r="I2750" t="s">
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -80136,24 +80136,53 @@
         <v>46323.3333333333</v>
       </c>
       <c r="C2751" t="n">
-        <v>49778.3515625</v>
+        <v>49778</v>
       </c>
       <c r="D2751" t="n">
-        <v>49857.5703125</v>
+        <v>49858</v>
       </c>
       <c r="E2751" t="n">
-        <v>49417.75</v>
+        <v>49418</v>
       </c>
       <c r="F2751" t="n">
-        <v>49824.30078125</v>
+        <v>49824</v>
       </c>
       <c r="G2751" t="n">
-        <v>49824.30078125</v>
+        <v>49824</v>
       </c>
       <c r="H2751" t="n">
+        <v>256975800</v>
+      </c>
+      <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>49830.6015625</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>50145.37109375</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>49566.5390625</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>50002.359375</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>50002.359375</v>
+      </c>
+      <c r="H2752" t="n">
         <v>0</v>
       </c>
-      <c r="I2751" t="s">
+      <c r="I2752" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FTSEMIB.MI.xlsx
+++ b/data/FTSEMIB.MI.xlsx
@@ -80165,24 +80165,53 @@
         <v>46324.3333333333</v>
       </c>
       <c r="C2752" t="n">
-        <v>49830.6015625</v>
+        <v>49831</v>
       </c>
       <c r="D2752" t="n">
-        <v>50145.37109375</v>
+        <v>50145</v>
       </c>
       <c r="E2752" t="n">
-        <v>49566.5390625</v>
+        <v>49567</v>
       </c>
       <c r="F2752" t="n">
-        <v>50002.359375</v>
+        <v>50002</v>
       </c>
       <c r="G2752" t="n">
-        <v>50002.359375</v>
+        <v>50002</v>
       </c>
       <c r="H2752" t="n">
+        <v>230379600</v>
+      </c>
+      <c r="I2752" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2753" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2753" t="n">
+        <v>49672.78125</v>
+      </c>
+      <c r="D2753" t="n">
+        <v>49700.2890625</v>
+      </c>
+      <c r="E2753" t="n">
+        <v>49339.73828125</v>
+      </c>
+      <c r="F2753" t="n">
+        <v>49500.96875</v>
+      </c>
+      <c r="G2753" t="n">
+        <v>49500.96875</v>
+      </c>
+      <c r="H2753" t="n">
         <v>0</v>
       </c>
-      <c r="I2752" t="s">
+      <c r="I2753" t="s">
         <v>9</v>
       </c>
     </row>
